--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N44" headerRowCount="1">
-  <autoFilter ref="A10:N44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N45" headerRowCount="1">
+  <autoFilter ref="A10:N45"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2583</v>
+        <v>3400</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2124</v>
+        <v>2766</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>800</v>
+        <v>1124</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>778</v>
+        <v>1030</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>685</v>
+        <v>941</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>175</v>
+        <v>233</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>183</v>
+        <v>303</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>677</v>
+        <v>901</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>342</v>
+        <v>438</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>402</v>
+        <v>519</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>389</v>
+        <v>527</v>
       </c>
       <c r="G12" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>372</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>396</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="H12" s="12" t="n">
-        <v>273</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>301</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>116</v>
-      </c>
       <c r="K12" s="12" t="n">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>354</v>
+        <v>458</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>195</v>
+        <v>282</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1</v>
@@ -983,85 +983,85 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>182</v>
+        <v>252</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>113</v>
+        <v>203</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,54 +1072,54 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="K18" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="M18" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L18" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>05239</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>SAN MINIATO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,47 +1361,47 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K21" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="L21" s="12" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05239</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SAN MINIATO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,35 +1411,35 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,31 +1523,31 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
@@ -1643,23 +1643,23 @@
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1681,31 +1681,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1716,12 +1716,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1731,35 +1731,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1770,50 +1770,46 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>BORGO A MOZZANO</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L29" s="12" t="n">
-        <v>55</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1843,47 +1839,47 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>18</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1893,86 +1889,86 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -1986,32 +1982,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>0</v>
@@ -2020,70 +2016,74 @@
         <v>20</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr"/>
+          <t>COLLESALVETTI</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J34" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2109,31 +2109,31 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I35" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="M35" s="12" t="n">
         <v>8</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K35" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="M35" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2144,133 +2144,129 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+          <t>COLLESALVETTI</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr"/>
+          <t>SAN GIOVANNI TEATINO</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L37" s="12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>05160</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>ORICOLA</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>1</v>
@@ -2279,19 +2275,19 @@
         <v>1</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2302,46 +2298,50 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>05160</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ORICOLA</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
+          <t>BORGO A MOZZANO</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>0</v>
@@ -2383,16 +2383,16 @@
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
@@ -2406,85 +2406,85 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>01300</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>MONTIGNOSO</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>01300</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>FERENTINO</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
+          <t>COLLESALVETTI</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>0</v>
@@ -2503,19 +2503,19 @@
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>54055</t>
+          <t>26646</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>FERENTINO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr"/>
@@ -2528,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>0</v>
@@ -2560,52 +2560,102 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>54055</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>POMEZIA</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>ERANDO FABIO</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
           <t>53624</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>FOLLONICA</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="G44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="12" t="n">
+      <c r="E45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="I45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>438</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.0593607305936073</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>458</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.2620087336244541</v>
+        <v>120</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>182</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.005494505494505495</v>
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>169</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.0650887573964497</v>
+        <v>11</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>203</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.7684729064039408</v>
+        <v>156</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>151</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.03311258278145696</v>
+        <v>5</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>164</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.8780487804878049</v>
+        <v>144</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>104</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.09615384615384616</v>
+        <v>10</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>208</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.09615384615384616</v>
+        <v>20</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>83</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.04819277108433735</v>
+        <v>4</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>111</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>3</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>64</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.1875</v>
+        <v>12</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>69</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.08695652173913043</v>
+        <v>6</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>126</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.4444444444444444</v>
+        <v>56</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>91</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.03296703296703297</v>
+        <v>3</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>63</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.01587301587301587</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>72</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.25</v>
+        <v>18</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>16</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.25</v>
+        <v>4</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>72</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.09722222222222222</v>
+        <v>7</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>47</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.0851063829787234</v>
+        <v>4</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>32</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.25</v>
+        <v>8</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.05882352941176471</v>
+        <v>2</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>9</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.1111111111111111</v>
+        <v>1</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>3</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3400</v>
+        <v>3574</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2766</v>
+        <v>2909</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1124</v>
+        <v>1220</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1030</v>
+        <v>1080</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>941</v>
+        <v>1004</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>303</v>
+        <v>333</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>901</v>
+        <v>947</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>438</v>
+        <v>458</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>26</v>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>527</v>
+        <v>562</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>372</v>
+        <v>401</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>458</v>
+        <v>484</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>2</v>
@@ -1157,19 +1157,19 @@
         <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J18" s="12" t="n">
         <v>62</v>
@@ -1220,14 +1220,14 @@
         <v>19</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>10</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1253,28 +1253,28 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>34</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>20</v>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>16</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J23" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L23" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="M23" s="12" t="n">
         <v>13</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,50 +1504,50 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>FROSINONE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1558,54 +1558,54 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FROSINONE</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>205</v>
+        <v>78</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="J25" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H25" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K25" s="12" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0</v>
@@ -1649,17 +1649,17 @@
         <v>10</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1681,28 +1681,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>1</v>
@@ -1735,31 +1735,31 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
@@ -1806,10 +1806,10 @@
         <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1839,16 +1839,16 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>18</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>23</v>
@@ -1857,10 +1857,10 @@
         <v>7</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1874,108 +1874,108 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
         <v>27</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2001,7 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>0</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>2</v>
@@ -2022,7 +2022,7 @@
         <v>2</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -2112,7 +2112,7 @@
         <v>18</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>8</v>
@@ -2130,7 +2130,7 @@
         <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>8</v>
@@ -2159,22 +2159,22 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="J36" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>3</v>
@@ -2216,7 +2216,7 @@
         <v>12</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1</v>
@@ -2234,14 +2234,14 @@
         <v>1</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
         <v>2</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>8</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>4</v>
@@ -2352,50 +2352,46 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>05241</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>SAN GIULIANO TERME</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+          <t>MONTIGNOSO</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2406,34 +2402,38 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>05241</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>MONTIGNOSO</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr"/>
+          <t>SAN GIULIANO TERME</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
@@ -2442,14 +2442,14 @@
         <v>0</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -1674,7 +1674,11 @@
           <t>MONSUMMANO TERME</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
@@ -1778,7 +1782,11 @@
           <t>BORGO A MOZZANO</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
@@ -2152,7 +2160,11 @@
           <t>COLLESALVETTI</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
           <t>MUFFATO LORENZO</t>
@@ -2256,7 +2268,11 @@
           <t>ORICOLA</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>PACI CLAUDIO</t>
@@ -2360,7 +2376,11 @@
           <t>MONTIGNOSO</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Tino Vincenzo</t>
+        </is>
+      </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
@@ -2518,7 +2538,11 @@
           <t>FERENTINO</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
@@ -2568,7 +2592,11 @@
           <t>POMEZIA</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3574</v>
+        <v>3809</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2909</v>
+        <v>3093</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1220</v>
+        <v>1316</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1080</v>
+        <v>1126</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1004</v>
+        <v>1062</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>947</v>
+        <v>988</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>546</v>
+        <v>574</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>417</v>
+        <v>440</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>121</v>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1</v>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>38</v>
@@ -1112,7 +1112,7 @@
         <v>21</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>6</v>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>2</v>
@@ -1157,19 +1157,19 @@
         <v>8</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>64</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>37</v>
+        <v>259</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,39 +1249,39 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>249</v>
+        <v>38</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>224</v>
+        <v>115</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>16</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>5</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>27</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>5</v>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>27</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,120 +1450,120 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>FROSINONE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>87</v>
+        <v>213</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FROSINONE</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>207</v>
+        <v>79</v>
       </c>
       <c r="G24" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H24" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I24" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="J24" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="H24" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I24" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K24" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>04951</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>GROSSETO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>04951</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>GROSSETO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1739,28 +1739,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>19</v>
@@ -1793,143 +1793,143 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>5</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
         <v>27</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>11</v>
@@ -2030,14 +2030,14 @@
         <v>2</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>3</v>
@@ -2084,10 +2084,10 @@
         <v>11</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2120,13 +2120,13 @@
         <v>18</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>14</v>
@@ -2138,7 +2138,7 @@
         <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>8</v>
@@ -2171,35 +2171,35 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J36" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K36" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>19</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>16</v>
@@ -2282,10 +2282,10 @@
         <v>9</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>1</v>
@@ -2294,20 +2294,20 @@
         <v>11</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>1</v>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>1</v>
@@ -2408,14 +2408,14 @@
         <v>2</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>3809</v>
+        <v>4043</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3093</v>
+        <v>3293</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1316</v>
+        <v>1413</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1126</v>
+        <v>1177</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1062</v>
+        <v>1167</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>361</v>
+        <v>408</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>988</v>
+        <v>1037</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>574</v>
+        <v>606</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>590</v>
+        <v>639</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -929,28 +929,28 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>1</v>
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>180</v>
@@ -1001,10 +1001,10 @@
         <v>109</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>18</v>
@@ -1037,47 +1037,47 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,89 +1087,89 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>140</v>
+        <v>272</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>167</v>
+        <v>246</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="F17" s="12" t="n">
         <v>152</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>127</v>
-      </c>
       <c r="G17" s="12" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>8</v>
+        <v>117</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>159</v>
+        <v>7</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,54 +1180,54 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>259</v>
+        <v>130</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>22</v>
+        <v>160</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>5</v>
@@ -1342,104 +1342,104 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J22" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K22" s="12" t="n">
         <v>27</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>140</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,50 +1450,50 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FROSINONE</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Funari Emanuele</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>213</v>
+        <v>108</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>103</v>
+        <v>151</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,105 +1519,105 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04516</t>
+          <t>16649</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CARRARA</t>
+          <t>FROSINONE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Funari Emanuele</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>90</v>
+        <v>220</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>04516</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>CARRARA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,39 +1627,39 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>10</v>
@@ -1706,10 +1706,10 @@
         <v>16</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>2</v>
@@ -1751,19 +1751,19 @@
         <v>11</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,35 +1793,35 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>5</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1850,13 +1850,13 @@
         <v>34</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>34</v>
@@ -1868,14 +1868,14 @@
         <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,13 +1904,13 @@
         <v>32</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>18</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>24</v>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1958,44 +1958,44 @@
         <v>27</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2009,35 +2009,35 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2063,16 +2063,16 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>14</v>
@@ -2081,13 +2081,13 @@
         <v>3</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,39 +2167,39 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2228,13 +2228,13 @@
         <v>15</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>14</v>
@@ -2246,14 +2246,14 @@
         <v>4</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2336,7 @@
         <v>8</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>1</v>
@@ -2498,13 +2498,13 @@
         <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4043</v>
+        <v>4361</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3293</v>
+        <v>3559</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1413</v>
+        <v>1554</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>1177</v>
+        <v>1251</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1167</v>
+        <v>1245</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>282</v>
+        <v>311</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>408</v>
+        <v>440</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1037</v>
+        <v>1105</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,35 +875,35 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>535</v>
+        <v>567</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>222</v>
+        <v>241</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1018,50 +1018,50 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>05054</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ROSIGNANO MARITTIMO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>237</v>
+        <v>190</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>180</v>
+        <v>7</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,66 +1072,66 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>272</v>
+        <v>124</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>39</v>
+        <v>108</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>120</v>
+        <v>154</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05054</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ROSIGNANO MARITTIMO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,89 +1141,89 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>152</v>
+        <v>286</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>160</v>
+        <v>17</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,54 +1234,54 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>40</v>
+        <v>141</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>167</v>
+        <v>7</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>132</v>
+        <v>207</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>16</v>
+        <v>160</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,28 +1307,28 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>5</v>
@@ -1342,104 +1342,104 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>88</v>
+        <v>153</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>34802</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>PRATO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PRATO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,39 +1519,39 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>93</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,19 +1577,19 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>6</v>
@@ -1598,7 +1598,7 @@
         <v>31</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>1</v>
@@ -1643,7 +1643,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>16</v>
@@ -1652,10 +1652,10 @@
         <v>28</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,35 +1685,35 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1739,31 +1739,31 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,35 +1793,35 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1847,28 +1847,28 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>1</v>
@@ -1901,13 +1901,13 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>27</v>
@@ -1919,7 +1919,7 @@
         <v>7</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>39</v>
@@ -1955,28 +1955,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -2012,13 +2012,13 @@
         <v>27</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>18</v>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>3</v>
@@ -2084,10 +2084,10 @@
         <v>12</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,39 +2167,39 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
         <v>19</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
         <v>15</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>1</v>
@@ -2246,14 +2246,14 @@
         <v>4</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>7</v>
@@ -2297,10 +2297,10 @@
         <v>3</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -2408,14 +2408,14 @@
         <v>2</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -810,11 +810,7 @@
           <t>PRATO</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Tino Vincenzo</t>
-        </is>
-      </c>
+      <c r="C11" s="2" t="inlineStr"/>
       <c r="D11" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
@@ -2538,11 +2534,7 @@
           <t>FERENTINO</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C43" s="2" t="inlineStr"/>
       <c r="D43" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
@@ -2592,11 +2584,7 @@
           <t>POMEZIA</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="inlineStr"/>
       <c r="D44" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N45" headerRowCount="1">
-  <autoFilter ref="A10:N45"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O45" headerRowCount="1">
+  <autoFilter ref="A10:O45"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:O45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -810,40 +826,45 @@
           <t>PRATO</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>VIALE NAM DINH  N 4 - LATO OVEST</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>1251</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>1245</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>311</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>440</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>1105</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>486</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>544</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -862,42 +883,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>R.A. FI-MARE / VIA NICCOLO' MACCHIAVELLI 287</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>651</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>661</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>497</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>187</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>567</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -916,42 +942,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>FRAZ-S-VITO STR-PROV</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>303</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>393</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>243</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -970,42 +1001,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>VIA CISANELLO 170</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>226</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>312</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>225</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>198</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>212</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1024,42 +1060,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>VIA AURELIA, 340</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>MUFFATO LORENZO</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>174</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>190</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1078,42 +1119,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>VIA DI TOR VERGATA</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1132,42 +1178,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>MACALLE', 26</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>286</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1186,42 +1237,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>CIULLA VALERIO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>171</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>149</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1240,42 +1296,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>VIA DI ACILIA</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>167</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1294,42 +1355,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>VIA PANNOCCHIA 90 - LOC. PONTE A EGOLA</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>CIULLA VALERIO</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1348,42 +1414,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>VIA P. SORIANO</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1402,42 +1473,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>XVI APRILE</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1456,42 +1532,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>DELLA COSTITUZIONE, 138</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="F23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="H23" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1510,42 +1591,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>VIALE UNITA' D'ITALIA 121</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>MUFFATO LORENZO</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1564,42 +1650,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>VIALE VOLSCI KM 5,81</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>Funari Emanuele</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>225</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>115</v>
       </c>
-      <c r="M25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="N25" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1618,42 +1709,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>VIA GALILEO GALILEI</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1672,42 +1768,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>VIA AURELIA NORD 162</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1726,42 +1827,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1780,42 +1886,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>VIA LUDOVICA</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1834,42 +1945,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>VIA PARIDE STEFANINI 3</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1888,42 +2004,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>CIULLA VALERIO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="N31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1942,42 +2063,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1996,42 +2122,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>VIA VARIANTE AURELIA KM273</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>7</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L33" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2050,42 +2181,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>DE LUCA ANTONIO</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2104,42 +2240,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>UNITA' D'ITALIA 9</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2158,42 +2299,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>FRAZ-STAGNO SS-1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>MUFFATO LORENZO</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>15</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L36" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2212,42 +2358,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>PACI CLAUDIO</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2266,42 +2417,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>S.S.TIBURTINA VALERIA KM. 68+300</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>Marcelli Mirko</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>PACI CLAUDIO</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L38" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2320,42 +2476,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>VIA DELLA FONTANA 4/5</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J39" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2374,42 +2535,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M40" s="12" t="n">
+      <c r="N40" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2428,20 +2594,22 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>LOC. MADONNA DELL'ACQUA - SS AURELIA KM 339 + 79</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>CIULLA VALERIO</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
       </c>
@@ -2449,21 +2617,24 @@
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="M41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2482,29 +2653,31 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>P.TA FIORENTINA</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>CASCIARI PAOLO</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" s="12" t="n">
         <v>0</v>
       </c>
@@ -2517,7 +2690,10 @@
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2534,15 +2710,17 @@
           <t>FERENTINO</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>VIA CONSORTILE ASI 7</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F43" s="12" t="n">
         <v>0</v>
       </c>
@@ -2550,11 +2728,11 @@
         <v>0</v>
       </c>
       <c r="H43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J43" s="12" t="n">
         <v>0</v>
       </c>
@@ -2567,7 +2745,10 @@
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="N43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2584,27 +2765,29 @@
           <t>POMEZIA</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>SS 148 KM 33+163</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>ERANDO FABIO</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="G44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" s="12" t="n">
         <v>0</v>
       </c>
@@ -2617,7 +2800,10 @@
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="N44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2636,29 +2822,31 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>AURELIA LOCALITA RONDELLI</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
           <t>Tino Vincenzo</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>ANTONINI GABRIELE</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I45" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J45" s="12" t="n">
         <v>0</v>
       </c>
@@ -2671,7 +2859,10 @@
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="N45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4361</v>
+        <v>4537</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3559</v>
+        <v>3702</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1554</v>
+        <v>1634</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,31 +838,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1251</v>
+        <v>1320</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1245</v>
+        <v>1329</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>440</v>
+        <v>491</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1105</v>
+        <v>1168</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>486</v>
+        <v>520</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>544</v>
+        <v>575</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>661</v>
+        <v>707</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>455</v>
+        <v>494</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>567</v>
+        <v>597</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>53</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>7</v>
@@ -1133,35 +1133,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>108</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>180</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1192,28 +1192,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>22</v>
@@ -1251,28 +1251,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>17</v>
@@ -1310,28 +1310,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>8</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>160</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>19</v>
@@ -1381,19 +1381,19 @@
         <v>20</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1428,28 +1428,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>62</v>
@@ -1546,28 +1546,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
@@ -1605,31 +1605,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1667,13 +1667,13 @@
         <v>81</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J25" s="12" t="n">
         <v>36</v>
@@ -1685,7 +1685,7 @@
         <v>31</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>1</v>
@@ -1735,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>14</v>
@@ -1782,35 +1782,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>3</v>
@@ -1859,13 +1859,13 @@
         <v>5</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
@@ -1921,14 +1921,14 @@
         <v>1</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -2021,13 +2021,13 @@
         <v>34</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>24</v>
@@ -2039,7 +2039,7 @@
         <v>9</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>4</v>
@@ -2105,24 +2105,24 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA VARIANTE AURELIA KM273</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2132,35 +2132,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2171,17 +2171,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+          <t>VIA VARIANTE AURELIA KM273</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2191,32 +2191,32 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
         <v>27</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>7</v>
@@ -2254,31 +2254,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2313,22 +2313,22 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>4</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>1</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2452,14 +2452,14 @@
         <v>3</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2493,13 +2493,13 @@
         <v>8</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>4</v>
@@ -2670,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4537</v>
+        <v>4756</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3702</v>
+        <v>3888</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1634</v>
+        <v>1732</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1320</v>
+        <v>1383</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1329</v>
+        <v>1447</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>338</v>
+        <v>368</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>491</v>
+        <v>552</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1168</v>
+        <v>1228</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>520</v>
+        <v>550</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>575</v>
+        <v>616</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>31</v>
@@ -897,35 +897,35 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>681</v>
+        <v>720</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>707</v>
+        <v>765</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>494</v>
+        <v>545</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>597</v>
+        <v>632</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>5</v>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,31 +1074,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1109,118 +1109,118 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA DI TOR VERGATA</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>131</v>
+        <v>316</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="I16" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>301</v>
+      </c>
+      <c r="N16" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>256</v>
-      </c>
-      <c r="N16" s="12" t="n">
-        <v>180</v>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MACALLE', 26</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>305</v>
+        <v>139</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>22</v>
+        <v>180</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1251,35 +1251,35 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>45</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1310,35 +1310,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>160</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>6</v>
@@ -1428,28 +1428,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>62</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>59</v>
@@ -1558,16 +1558,16 @@
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
@@ -1605,28 +1605,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>11</v>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>6</v>
@@ -1685,7 +1685,7 @@
         <v>31</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>1</v>
@@ -1735,16 +1735,16 @@
         <v>2</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>14</v>
@@ -1782,19 +1782,19 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>10</v>
@@ -1803,10 +1803,10 @@
         <v>20</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>3</v>
@@ -1853,19 +1853,19 @@
         <v>13</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1900,35 +1900,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>5</v>
@@ -1980,7 +1980,7 @@
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -1994,17 +1994,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2014,56 +2014,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SS 1 VAR.AURELIA KM.223,2</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2136,31 +2136,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2198,13 +2198,13 @@
         <v>27</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>18</v>
@@ -2254,31 +2254,31 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2334,14 +2334,14 @@
         <v>4</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>4</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>1</v>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>19</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
         <v>8</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>1</v>
@@ -2570,7 +2570,7 @@
         <v>2</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>1</v>
@@ -2670,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4756</v>
+        <v>5013</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3888</v>
+        <v>4094</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1732</v>
+        <v>1857</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,35 +838,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1383</v>
+        <v>1470</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1447</v>
+        <v>1602</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>552</v>
+        <v>633</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1228</v>
+        <v>1308</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>550</v>
+        <v>589</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>616</v>
+        <v>656</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>720</v>
+        <v>752</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>765</v>
+        <v>845</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>545</v>
+        <v>591</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>632</v>
+        <v>664</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>428</v>
+        <v>467</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>8</v>
@@ -1109,17 +1109,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MACALLE', 26</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1129,157 +1129,157 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>316</v>
+        <v>47</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>301</v>
+        <v>156</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA DI TOR VERGATA</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>139</v>
+        <v>334</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="I17" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>161</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>331</v>
+      </c>
+      <c r="N17" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J17" s="12" t="n">
-        <v>162</v>
-      </c>
-      <c r="K17" s="12" t="n">
-        <v>97</v>
-      </c>
-      <c r="L17" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>272</v>
-      </c>
-      <c r="N17" s="12" t="n">
-        <v>180</v>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>45</v>
+        <v>156</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>146</v>
+        <v>282</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1310,35 +1310,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G19" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="H19" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>154</v>
-      </c>
       <c r="K19" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>22</v>
@@ -1381,23 +1381,23 @@
         <v>20</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>35</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1428,28 +1428,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>6</v>
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>62</v>
@@ -1546,35 +1546,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1605,28 +1605,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>11</v>
@@ -1664,28 +1664,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>80</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>54</v>
@@ -1744,14 +1744,14 @@
         <v>29</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>14</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1782,35 +1782,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1841,19 +1841,19 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>5</v>
@@ -1862,10 +1862,10 @@
         <v>30</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1900,28 +1900,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>6</v>
@@ -1935,55 +1935,55 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>04978</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SCARLINO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>SS 1 VAR.AURELIA KM.223,2</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1994,59 +1994,59 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>04978</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SCARLINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SS 1 VAR.AURELIA KM.223,2</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>25</v>
@@ -2095,7 +2095,7 @@
         <v>8</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>45</v>
@@ -2112,17 +2112,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2132,35 +2132,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2171,17 +2171,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA VARIANTE AURELIA KM273</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2191,35 +2191,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2230,17 +2230,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>VIA VARIANTE AURELIA KM273</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2250,35 +2250,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2313,35 +2313,35 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>17</v>
-      </c>
       <c r="K36" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2372,16 +2372,16 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37" s="12" t="n">
         <v>14</v>
@@ -2390,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>19</v>
@@ -2434,7 +2434,7 @@
         <v>10</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>2</v>
@@ -2452,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
@@ -2466,17 +2466,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05160</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>MONTIGNOSO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA FONTANA 4/5</t>
+          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,25 +2490,25 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>9</v>
@@ -2518,24 +2518,24 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>05160</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>MONTIGNOSO</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
+          <t>VIA DELLA FONTANA 4/5</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,35 +2549,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J40" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5013</v>
+        <v>5256</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4094</v>
+        <v>4294</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1857</v>
+        <v>1955</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,31 +838,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1470</v>
+        <v>1581</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1602</v>
+        <v>1675</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>408</v>
+        <v>450</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>633</v>
+        <v>670</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1308</v>
+        <v>1397</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>589</v>
+        <v>637</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>656</v>
+        <v>693</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>752</v>
+        <v>775</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>845</v>
+        <v>886</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>591</v>
+        <v>622</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>567</v>
+        <v>590</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>174</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>6</v>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1077,13 +1077,13 @@
         <v>226</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>86</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>187</v>
@@ -1109,17 +1109,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1129,56 +1129,56 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>47</v>
+        <v>348</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>207</v>
+        <v>55</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>156</v>
+        <v>353</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>MACALLE', 26</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1188,39 +1188,39 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>334</v>
+        <v>51</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>53</v>
+        <v>208</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>331</v>
+        <v>162</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1251,28 +1251,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>100</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>180</v>
@@ -1310,35 +1310,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>161</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>7</v>
@@ -1428,31 +1428,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1487,31 +1487,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1546,19 +1546,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>25</v>
@@ -1567,14 +1567,14 @@
         <v>6</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1605,31 +1605,31 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>100</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1664,19 +1664,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>17</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>7</v>
@@ -1685,7 +1685,7 @@
         <v>32</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1723,28 +1723,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>14</v>
@@ -1782,31 +1782,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1817,17 +1817,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1837,56 +1837,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>32</v>
-      </c>
       <c r="K28" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1896,39 +1896,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1959,153 +1959,153 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>62</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="K32" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2136,16 +2136,16 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>27</v>
@@ -2157,10 +2157,10 @@
         <v>6</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2195,31 +2195,31 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2230,17 +2230,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>54101</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>CECINA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA VARIANTE AURELIA KM273</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2250,56 +2250,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ANTONINI GABRIELE</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>54101</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>CECINA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-STAGNO SS-1</t>
+          <t>VIA VARIANTE AURELIA KM273</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2309,39 +2309,39 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>ANTONINI GABRIELE</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2431,19 +2431,19 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H38" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="J38" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>3</v>
@@ -2452,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2552,13 +2552,13 @@
         <v>8</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>4</v>
@@ -2670,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5256</v>
+        <v>5536</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4294</v>
+        <v>4532</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1955</v>
+        <v>2080</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,35 +838,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1581</v>
+        <v>1675</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1675</v>
+        <v>1749</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>450</v>
+        <v>488</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1397</v>
+        <v>1485</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>637</v>
+        <v>684</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>693</v>
+        <v>727</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>36</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>775</v>
+        <v>815</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>886</v>
+        <v>941</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>663</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <v>622</v>
       </c>
-      <c r="J12" s="12" t="n">
-        <v>590</v>
-      </c>
       <c r="K12" s="12" t="n">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>705</v>
+        <v>739</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>128</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>494</v>
+        <v>522</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>6</v>
@@ -1015,31 +1015,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>277</v>
+        <v>306</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>238</v>
+        <v>266</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,28 +1074,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>8</v>
@@ -1133,28 +1133,28 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>40</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>26</v>
@@ -1168,118 +1168,118 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>208</v>
+        <v>117</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>162</v>
+        <v>296</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA DI TOR VERGATA</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>285</v>
+        <v>165</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1310,35 +1310,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>161</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>7</v>
@@ -1428,35 +1428,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>67</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>61</v>
@@ -1522,17 +1522,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>DELLA COSTITUZIONE, 138</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1542,35 +1542,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="G23" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="H23" s="12" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1581,17 +1581,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIALE UNITA' D'ITALIA 121</t>
+          <t>DELLA COSTITUZIONE, 138</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1601,35 +1601,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1664,28 +1664,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1723,31 +1723,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>80</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>9</v>
@@ -1803,14 +1803,14 @@
         <v>24</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>14</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1841,35 +1841,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="G28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>62</v>
-      </c>
       <c r="K28" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1900,31 +1900,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>7</v>
@@ -1971,141 +1971,141 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>34201</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>SANTA CROCE SULL'ARNO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>34201</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SANTA CROCE SULL'ARNO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>VIA PROVINCIALE NUOVA FRANCESCA KM 8,000 SNC</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>35</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J33" s="12" t="n">
         <v>27</v>
@@ -2157,10 +2157,10 @@
         <v>6</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05099</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2191,46 +2191,46 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H34" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K34" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="N34" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L34" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="N34" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>05099</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-STAGNO SS-1</t>
+          <t>S.G.C. FI/PI/LI LOC.GRECCIANO SUD 64</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2250,39 +2250,39 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2316,13 +2316,13 @@
         <v>27</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>18</v>
@@ -2375,7 +2375,7 @@
         <v>18</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>1</v>
@@ -2393,7 +2393,7 @@
         <v>8</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2452,14 +2452,14 @@
         <v>3</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2552,13 +2552,13 @@
         <v>8</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>4</v>
@@ -2611,13 +2611,13 @@
         <v>5</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
@@ -2670,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5536</v>
+        <v>5770</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4532</v>
+        <v>4725</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2080</v>
+        <v>2213</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,35 +838,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1675</v>
+        <v>1722</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1749</v>
+        <v>1823</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>488</v>
+        <v>509</v>
       </c>
       <c r="I11" s="12" t="n">
+        <v>745</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>1530</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <v>707</v>
       </c>
-      <c r="J11" s="12" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>684</v>
-      </c>
       <c r="L11" s="12" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>727</v>
+        <v>773</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -897,28 +897,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>815</v>
+        <v>859</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>941</v>
+        <v>983</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>663</v>
+        <v>695</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>622</v>
+        <v>652</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>739</v>
+        <v>780</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>128</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>522</v>
+        <v>547</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>70</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         <v>306</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>266</v>
@@ -1036,7 +1036,7 @@
         <v>44</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>45</v>
@@ -1074,31 +1074,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1109,17 +1109,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05349</t>
+          <t>05245</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>PISTOIA</t>
+          <t>VECCHIANO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>MACALLE', 26</t>
+          <t>VIA PROV.LE VECCHIANESE 38</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1129,157 +1129,157 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CIULLA VALERIO</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>362</v>
+        <v>61</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>59</v>
+        <v>244</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>378</v>
+        <v>191</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>05349</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PISTOIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA DI TOR VERGATA</t>
+          <t>MACALLE', 26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>173</v>
+        <v>371</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>296</v>
+        <v>406</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>180</v>
+        <v>29</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05245</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VECCHIANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA PROV.LE VECCHIANESE 38</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>CIULLA VALERIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>104</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>165</v>
+        <v>306</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1310,35 +1310,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>161</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>21</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>7</v>
@@ -1428,35 +1428,35 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>8</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1487,28 +1487,28 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>61</v>
@@ -1546,31 +1546,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1605,35 +1605,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1664,28 +1664,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>32</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1726,13 +1726,13 @@
         <v>90</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>60</v>
@@ -1744,7 +1744,7 @@
         <v>33</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>15</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H27" s="12" t="n">
         <v>9</v>
@@ -1800,34 +1800,34 @@
         <v>12</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>05290</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BORGO A MOZZANO</t>
+          <t>PONTEDERA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA LUDOVICA</t>
+          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1837,56 +1837,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>64</v>
+        <v>39</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>05290</t>
+          <t>55491</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>PONTEDERA</t>
+          <t>BORGO A MOZZANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>S.G.C. FIPILI KM 52,800 - LOC. CURIGLIANO</t>
+          <t>VIA LUDOVICA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1896,39 +1896,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>118</v>
+        <v>42</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1959,35 +1959,35 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2018,19 +2018,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>21</v>
@@ -2039,7 +2039,7 @@
         <v>4</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>1</v>
@@ -2077,28 +2077,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2136,31 +2136,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>37</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2216,14 +2216,14 @@
         <v>9</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>5</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2257,13 +2257,13 @@
         <v>33</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J35" s="12" t="n">
         <v>20</v>
@@ -2275,7 +2275,7 @@
         <v>13</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>17</v>
@@ -2316,13 +2316,13 @@
         <v>27</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>18</v>
@@ -2372,28 +2372,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>33</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2434,7 +2434,7 @@
         <v>12</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>3</v>
@@ -2452,14 +2452,14 @@
         <v>3</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2490,28 +2490,28 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="K39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>1</v>
@@ -2552,13 +2552,13 @@
         <v>8</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>4</v>
@@ -2611,13 +2611,13 @@
         <v>5</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
@@ -2670,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>35</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5770</v>
+        <v>6099</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4725</v>
+        <v>5022</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2213</v>
+        <v>2397</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,35 +838,35 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1722</v>
+        <v>1827</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1823</v>
+        <v>1886</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>509</v>
+        <v>555</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>745</v>
+        <v>786</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1530</v>
+        <v>1625</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>707</v>
+        <v>757</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>773</v>
+        <v>815</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -897,31 +897,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>859</v>
+        <v>931</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>983</v>
+        <v>1032</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>695</v>
+        <v>733</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>652</v>
+        <v>717</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>259</v>
+        <v>292</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>780</v>
+        <v>841</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>378</v>
+        <v>391</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>266</v>
@@ -1033,13 +1033,13 @@
         <v>161</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1074,31 +1074,31 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
+        <v>264</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>221</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>258</v>
       </c>
-      <c r="G15" s="12" t="n">
-        <v>212</v>
-      </c>
-      <c r="H15" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>182</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>216</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>241</v>
-      </c>
       <c r="N15" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1133,35 +1133,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1192,31 +1192,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>41</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA DI TOR VERGATA</t>
+          <t>VIA DI ACILIA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1247,46 +1247,46 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>117</v>
+        <v>24</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA DI ACILIA</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1306,35 +1306,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1369,28 +1369,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>7</v>
@@ -1428,31 +1428,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>42</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1487,31 +1487,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1522,17 +1522,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>53676</t>
+          <t>55416</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>PIOMBINO</t>
+          <t>MONSUMMANO TERME</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIALE UNITA' D'ITALIA 121</t>
+          <t>DELLA COSTITUZIONE, 138</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1542,56 +1542,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>DE LUCA ANTONIO</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>55416</t>
+          <t>53676</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>MONSUMMANO TERME</t>
+          <t>PIOMBINO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>DELLA COSTITUZIONE, 138</t>
+          <t>VIALE UNITA' D'ITALIA 121</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1601,39 +1601,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>DE LUCA ANTONIO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1664,28 +1664,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>71</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
@@ -1723,28 +1723,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>15</v>
@@ -1782,28 +1782,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>26</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>16</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>6</v>
@@ -1853,16 +1853,16 @@
         <v>14</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>34</v>
@@ -1900,35 +1900,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1959,28 +1959,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -2018,31 +2018,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>5</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>11</v>
@@ -2098,10 +2098,10 @@
         <v>10</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>05055</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>PIETRASANTA</t>
+          <t>COLLESALVETTI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>UNITA' D'ITALIA 9</t>
+          <t>FRAZ-STAGNO SS-1</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2132,56 +2132,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>MUFFATO LORENZO</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05055</t>
+          <t>54066</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>COLLESALVETTI</t>
+          <t>PIETRASANTA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-STAGNO SS-1</t>
+          <t>UNITA' D'ITALIA 9</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2191,39 +2191,39 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MUFFATO LORENZO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2257,10 +2257,10 @@
         <v>33</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>32</v>
@@ -2275,10 +2275,10 @@
         <v>13</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2316,13 +2316,13 @@
         <v>27</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>18</v>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>33</v>
@@ -2384,7 +2384,7 @@
         <v>6</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>0</v>
@@ -2393,57 +2393,57 @@
         <v>10</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ORICOLA</t>
+          <t>MONTIGNOSO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>S.S.TIBURTINA VALERIA KM. 68+300</t>
+          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>CASCIARI PAOLO</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="I38" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>3</v>
@@ -2452,10 +2452,10 @@
         <v>3</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2466,55 +2466,55 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MONTIGNOSO</t>
+          <t>ORICOLA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA AURELIA KM 376 LOC. DEBBIA</t>
+          <t>S.S.TIBURTINA VALERIA KM. 68+300</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Marcelli Mirko</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>CASCIARI PAOLO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         <v>8</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>1</v>
@@ -2611,13 +2611,13 @@
         <v>5</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>1</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - PACIARONI ALESSANDRO.xlsx
@@ -684,13 +684,13 @@
         <v>10</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>877</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>152</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>266</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>161</v>
@@ -863,7 +863,7 @@
         <v>45</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>47</v>
@@ -904,7 +904,7 @@
         <v>221</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>24</v>
@@ -913,7 +913,7 @@
         <v>12</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>89</v>
@@ -922,10 +922,10 @@
         <v>24</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>120</v>
@@ -972,7 +972,7 @@
         <v>35</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>107</v>
@@ -981,14 +981,14 @@
         <v>31</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>61</v>
@@ -1031,7 +1031,7 @@
         <v>74</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>39</v>
@@ -1040,7 +1040,7 @@
         <v>42</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>9</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>252</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>71</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>13</v>
@@ -1099,7 +1099,7 @@
         <v>36</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>73</v>
@@ -1149,7 +1149,7 @@
         <v>5</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>24</v>
@@ -1158,14 +1158,14 @@
         <v>4</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N16" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>3</v>
@@ -1208,7 +1208,7 @@
         <v>6</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>10</v>
@@ -1267,7 +1267,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>3</v>
@@ -1276,14 +1276,14 @@
         <v>3</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>0</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1368,13 +1368,13 @@
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
